--- a/Produto-2025-11-17-oooooo.xlsx
+++ b/Produto-2025-11-17-oooooo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Azzure\Farmacia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\pharmaSys-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A52B99-BA0E-4856-A38D-FD4E411DB9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEC380C-9D7B-4607-BD89-217042F08ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19310" yWindow="740" windowWidth="19420" windowHeight="11020" xr2:uid="{1FD696F9-A63E-4372-86E0-8599A472E569}"/>
   </bookViews>
